--- a/backend/outputs/output_basicat/GRC/prod/GRC_prod-FR.xlsx
+++ b/backend/outputs/output_basicat/GRC/prod/GRC_prod-FR.xlsx
@@ -428,7 +428,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
     <col width="25" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
   </cols>
@@ -538,7 +538,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10.20.1.10</t>
+          <t>10.20.1.73</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -573,12 +573,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>SG_INFRA</t>
+          <t>SG-OP-M5W-SQLSERVE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>10008</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>10001</t>
         </is>
       </c>
     </row>
